--- a/projection_library_kernel_v1.1/projection_library/sample_data/tier2_industrial_clean.xlsx
+++ b/projection_library_kernel_v1.1/projection_library/sample_data/tier2_industrial_clean.xlsx
@@ -729,25 +729,25 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Utile di esercizio</t>
+          <t>Ricavi prodotti</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SP_equity</t>
+          <t>P&amp;L</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-238</v>
+        <v>1720</v>
       </c>
       <c r="D18" t="n">
-        <v>-265</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ricavi prodotti</t>
+          <t>Ricavi servizi</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -756,16 +756,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1720</v>
+        <v>160</v>
       </c>
       <c r="D19" t="n">
-        <v>1900</v>
+        <v>200</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ricavi servizi</t>
+          <t>Materie prime</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>160</v>
+        <v>-610</v>
       </c>
       <c r="D20" t="n">
-        <v>200</v>
+        <v>-680</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Materie prime</t>
+          <t>Manodopera diretta</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -792,16 +792,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-610</v>
+        <v>-280</v>
       </c>
       <c r="D21" t="n">
-        <v>-680</v>
+        <v>-310</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Manodopera diretta</t>
+          <t>Costi commerciali</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -810,16 +810,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-280</v>
+        <v>-95</v>
       </c>
       <c r="D22" t="n">
-        <v>-310</v>
+        <v>-105</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Costi commerciali</t>
+          <t>Costi generali e amministrativi</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -828,46 +828,46 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-95</v>
+        <v>-72</v>
       </c>
       <c r="D23" t="n">
-        <v>-105</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Costi generali e amministrativi</t>
+          <t>Fondi rischi</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>P&amp;L</t>
+          <t>SP_liabilities</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-72</v>
+        <v>-45</v>
       </c>
       <c r="D24" t="n">
-        <v>-75</v>
+        <v>-52</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Fondi rischi</t>
+          <t>Crediti per imposte anticipate</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SP_liabilities</t>
+          <t>SP_assets</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-45</v>
+        <v>11</v>
       </c>
       <c r="D25" t="n">
-        <v>-52</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/projection_library_kernel_v1.1/projection_library/sample_data/tier2_industrial_clean.xlsx
+++ b/projection_library_kernel_v1.1/projection_library/sample_data/tier2_industrial_clean.xlsx
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>162</v>
+        <v>197</v>
       </c>
       <c r="D12" t="n">
-        <v>180</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
